--- a/AHR_combined_data.xlsx
+++ b/AHR_combined_data.xlsx
@@ -40875,13 +40875,13 @@
         <v>1.731385488861424</v>
       </c>
       <c r="E1502">
-        <v>2.20420432952136</v>
+        <v>2.191241996366194</v>
       </c>
       <c r="F1502">
-        <v>0.7854922820323976</v>
+        <v>0.7901388763690342</v>
       </c>
       <c r="G1502">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="1503">
@@ -40902,13 +40902,13 @@
         <v>10.85917412642226</v>
       </c>
       <c r="E1503">
-        <v>2.20420432952136</v>
+        <v>2.191241996366194</v>
       </c>
       <c r="F1503">
-        <v>4.926573267724375</v>
+        <v>4.955716504352496</v>
       </c>
       <c r="G1503">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="1504">
@@ -40929,13 +40929,13 @@
         <v>5.158633032912483</v>
       </c>
       <c r="E1504">
-        <v>2.20420432952136</v>
+        <v>2.191241996366194</v>
       </c>
       <c r="F1504">
-        <v>2.340360629829937</v>
+        <v>2.354205077060045</v>
       </c>
       <c r="G1504">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="1505">
@@ -40956,13 +40956,13 @@
         <v>2.399072717960698</v>
       </c>
       <c r="E1505">
-        <v>2.20420432952136</v>
+        <v>2.191241996366194</v>
       </c>
       <c r="F1505">
-        <v>1.088407588094001</v>
+        <v>1.094846083608819</v>
       </c>
       <c r="G1505">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="1506">
@@ -40983,13 +40983,13 @@
         <v>7.292500101914317</v>
       </c>
       <c r="E1506">
-        <v>2.20420432952136</v>
+        <v>2.191241996366194</v>
       </c>
       <c r="F1506">
-        <v>3.308450130618278</v>
+        <v>3.328021329459594</v>
       </c>
       <c r="G1506">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="1507">
@@ -41010,13 +41010,13 @@
         <v>7.208684798054684</v>
       </c>
       <c r="E1507">
-        <v>2.20420432952136</v>
+        <v>2.191241996366194</v>
       </c>
       <c r="F1507">
-        <v>3.270424933617674</v>
+        <v>3.28977119369247</v>
       </c>
       <c r="G1507">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1508">
@@ -41037,10 +41037,10 @@
         <v>0.03388681802778719</v>
       </c>
       <c r="E1508">
-        <v>2.20420432952136</v>
+        <v>2.191241996366194</v>
       </c>
       <c r="F1508">
-        <v>0.01537371902138749</v>
+        <v>0.01546466254479549</v>
       </c>
       <c r="G1508">
         <v>1</v>
@@ -41061,7 +41061,7 @@
         </is>
       </c>
       <c r="E1509">
-        <v>2.20420432952136</v>
+        <v>2.191241996366194</v>
       </c>
     </row>
     <row r="1510">
@@ -41082,10 +41082,10 @@
         <v>0.1733549512754773</v>
       </c>
       <c r="E1510">
-        <v>2.20420432952136</v>
+        <v>2.191241996366194</v>
       </c>
       <c r="F1510">
-        <v>0.07864740530344617</v>
+        <v>0.07911264550558872</v>
       </c>
       <c r="G1510">
         <v>2</v>
@@ -41109,10 +41109,10 @@
         <v>0.7580686936581237</v>
       </c>
       <c r="E1511">
-        <v>2.20420432952136</v>
+        <v>2.191241996366194</v>
       </c>
       <c r="F1511">
-        <v>0.3439194286596548</v>
+        <v>0.3459538904946386</v>
       </c>
       <c r="G1511">
         <v>16</v>
@@ -41133,7 +41133,7 @@
         </is>
       </c>
       <c r="E1512">
-        <v>2.20420432952136</v>
+        <v>2.191241996366194</v>
       </c>
     </row>
     <row r="1513">
@@ -41154,10 +41154,10 @@
         <v>1.058758503352351</v>
       </c>
       <c r="E1513">
-        <v>2.20420432952136</v>
+        <v>2.191241996366194</v>
       </c>
       <c r="F1513">
-        <v>0.4803359149477122</v>
+        <v>0.4831773510676245</v>
       </c>
       <c r="G1513">
         <v>22</v>
@@ -41181,10 +41181,10 @@
         <v>1.325808474424438</v>
       </c>
       <c r="E1514">
-        <v>2.20420432952136</v>
+        <v>2.191241996366194</v>
       </c>
       <c r="F1514">
-        <v>0.6014907314479032</v>
+        <v>0.60504886115868</v>
       </c>
       <c r="G1514">
         <v>25</v>
@@ -41208,13 +41208,13 @@
         <v>2.14079563327743</v>
       </c>
       <c r="E1515">
-        <v>2.20420432952136</v>
+        <v>2.191241996366194</v>
       </c>
       <c r="F1515">
-        <v>0.9712328410779868</v>
+        <v>0.9769781871776732</v>
       </c>
       <c r="G1515">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="1516">
@@ -41235,13 +41235,13 @@
         <v>1.758128336987306</v>
       </c>
       <c r="E1516">
-        <v>2.20420432952136</v>
+        <v>2.191241996366194</v>
       </c>
       <c r="F1516">
-        <v>0.7976249358738358</v>
+        <v>0.8023433011519795</v>
       </c>
       <c r="G1516">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1517">
@@ -41262,10 +41262,10 @@
         <v>0.6238174877539552</v>
       </c>
       <c r="E1517">
-        <v>2.20420432952136</v>
+        <v>2.191241996366194</v>
       </c>
       <c r="F1517">
-        <v>0.2830125498798091</v>
+        <v>0.2846867159302585</v>
       </c>
       <c r="G1517">
         <v>13</v>
@@ -41289,10 +41289,10 @@
         <v>1.244698090608046</v>
       </c>
       <c r="E1518">
-        <v>2.20420432952136</v>
+        <v>2.191241996366194</v>
       </c>
       <c r="F1518">
-        <v>0.5646926983753501</v>
+        <v>0.5680331486308534</v>
       </c>
       <c r="G1518">
         <v>24</v>
@@ -41316,13 +41316,13 @@
         <v>4.549685709612211</v>
       </c>
       <c r="E1519">
-        <v>2.20420432952136</v>
+        <v>2.191241996366194</v>
       </c>
       <c r="F1519">
-        <v>2.064094353085754</v>
+        <v>2.076304541970763</v>
       </c>
       <c r="G1519">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="1520">
@@ -41343,10 +41343,10 @@
         <v>0.1933543397307362</v>
       </c>
       <c r="E1520">
-        <v>2.20420432952136</v>
+        <v>2.191241996366194</v>
       </c>
       <c r="F1520">
-        <v>0.08772069682519988</v>
+        <v>0.08823961025362868</v>
       </c>
       <c r="G1520">
         <v>3</v>
@@ -41370,13 +41370,13 @@
         <v>1.51333933697304</v>
       </c>
       <c r="E1521">
-        <v>2.20420432952136</v>
+        <v>2.191241996366194</v>
       </c>
       <c r="F1521">
-        <v>0.6865694421812787</v>
+        <v>0.6906308566021727</v>
       </c>
       <c r="G1521">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="1522">
@@ -41397,13 +41397,13 @@
         <v>2.014122818366372</v>
       </c>
       <c r="E1522">
-        <v>2.20420432952136</v>
+        <v>2.191241996366194</v>
       </c>
       <c r="F1522">
-        <v>0.9137641149646667</v>
+        <v>0.9191695037364453</v>
       </c>
       <c r="G1522">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="1523">
@@ -41424,13 +41424,13 @@
         <v>2.298412986503718</v>
       </c>
       <c r="E1523">
-        <v>2.20420432952136</v>
+        <v>2.191241996366194</v>
       </c>
       <c r="F1523">
-        <v>1.042740437318175</v>
+        <v>1.048908787945489</v>
       </c>
       <c r="G1523">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="1524">
@@ -41451,10 +41451,10 @@
         <v>0.5061183343323008</v>
       </c>
       <c r="E1524">
-        <v>2.20420432952136</v>
+        <v>2.191241996366194</v>
       </c>
       <c r="F1524">
-        <v>0.2296149805867606</v>
+        <v>0.2309732723138808</v>
       </c>
       <c r="G1524">
         <v>9</v>
@@ -41478,13 +41478,13 @@
         <v>1.813524357899032</v>
       </c>
       <c r="E1525">
-        <v>2.20420432952136</v>
+        <v>2.191241996366194</v>
       </c>
       <c r="F1525">
-        <v>0.8227569166842332</v>
+        <v>0.8276239506665428</v>
       </c>
       <c r="G1525">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="1526">
@@ -41505,10 +41505,10 @@
         <v>1.120792126283758</v>
       </c>
       <c r="E1526">
-        <v>2.20420432952136</v>
+        <v>2.191241996366194</v>
       </c>
       <c r="F1526">
-        <v>0.5084792327429719</v>
+        <v>0.5114871511875014</v>
       </c>
       <c r="G1526">
         <v>23</v>
@@ -41532,13 +41532,13 @@
         <v>1.492604821565878</v>
       </c>
       <c r="E1527">
-        <v>2.20420432952136</v>
+        <v>2.191241996366194</v>
       </c>
       <c r="F1527">
-        <v>0.6771626394046668</v>
+        <v>0.681168407707187</v>
       </c>
       <c r="G1527">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1528">
@@ -41559,10 +41559,10 @@
         <v>0.5662787055109763</v>
       </c>
       <c r="E1528">
-        <v>2.20420432952136</v>
+        <v>2.191241996366194</v>
       </c>
       <c r="F1528">
-        <v>0.2569084444335262</v>
+        <v>0.2584281911582811</v>
       </c>
       <c r="G1528">
         <v>12</v>
@@ -41586,10 +41586,10 @@
         <v>0.5323273346692246</v>
       </c>
       <c r="E1529">
-        <v>2.20420432952136</v>
+        <v>2.191241996366194</v>
       </c>
       <c r="F1529">
-        <v>0.2415054391916645</v>
+        <v>0.2429340691498245</v>
       </c>
       <c r="G1529">
         <v>10</v>
@@ -41613,10 +41613,10 @@
         <v>0.3884581319825349</v>
       </c>
       <c r="E1530">
-        <v>2.20420432952136</v>
+        <v>2.191241996366194</v>
       </c>
       <c r="F1530">
-        <v>0.1762350825555669</v>
+        <v>0.1772776044940391</v>
       </c>
       <c r="G1530">
         <v>5</v>
@@ -41640,10 +41640,10 @@
         <v>0.9135472370766489</v>
       </c>
       <c r="E1531">
-        <v>2.20420432952136</v>
+        <v>2.191241996366194</v>
       </c>
       <c r="F1531">
-        <v>0.414456692985003</v>
+        <v>0.4169084193309607</v>
       </c>
       <c r="G1531">
         <v>17</v>
@@ -41667,13 +41667,13 @@
         <v>2.894558860284633</v>
       </c>
       <c r="E1532">
-        <v>2.20420432952136</v>
+        <v>2.191241996366194</v>
       </c>
       <c r="F1532">
-        <v>1.313198972308154</v>
+        <v>1.32096722547522</v>
       </c>
       <c r="G1532">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1533">
@@ -41694,13 +41694,13 @@
         <v>2.081965796822538</v>
       </c>
       <c r="E1533">
-        <v>2.20420432952136</v>
+        <v>2.191241996366194</v>
       </c>
       <c r="F1533">
-        <v>0.9445430121601446</v>
+        <v>0.9501304740759474</v>
       </c>
       <c r="G1533">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="1534">
@@ -41721,10 +41721,10 @@
         <v>1.016120503452046</v>
       </c>
       <c r="E1534">
-        <v>2.20420432952136</v>
+        <v>2.191241996366194</v>
       </c>
       <c r="F1534">
-        <v>0.4609919733134247</v>
+        <v>0.4637189799835486</v>
       </c>
       <c r="G1534">
         <v>20</v>
@@ -41748,10 +41748,10 @@
         <v>0.4708121204987101</v>
       </c>
       <c r="E1535">
-        <v>2.20420432952136</v>
+        <v>2.191241996366194</v>
       </c>
       <c r="F1535">
-        <v>0.2135973122786426</v>
+        <v>0.2148608511882634</v>
       </c>
       <c r="G1535">
         <v>7</v>
@@ -41775,10 +41775,10 @@
         <v>0.9524788273159156</v>
       </c>
       <c r="E1536">
-        <v>2.20420432952136</v>
+        <v>2.191241996366194</v>
       </c>
       <c r="F1536">
-        <v>0.4321191164354282</v>
+        <v>0.4346753251787988</v>
       </c>
       <c r="G1536">
         <v>19</v>
@@ -41802,13 +41802,13 @@
         <v>1.714992322092129</v>
       </c>
       <c r="E1537">
-        <v>2.20420432952136</v>
+        <v>2.191241996366194</v>
       </c>
       <c r="F1537">
-        <v>0.7780550555694339</v>
+        <v>0.7826576548533456</v>
       </c>
       <c r="G1537">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="1538">
@@ -41829,10 +41829,10 @@
         <v>0.6886384748980169</v>
       </c>
       <c r="E1538">
-        <v>2.20420432952136</v>
+        <v>2.191241996366194</v>
       </c>
       <c r="F1538">
-        <v>0.3124204347459719</v>
+        <v>0.31426856369128</v>
       </c>
       <c r="G1538">
         <v>15</v>
@@ -41856,13 +41856,13 @@
         <v>2.671462200005628</v>
       </c>
       <c r="E1539">
-        <v>2.20420432952136</v>
+        <v>2.191241996366194</v>
       </c>
       <c r="F1539">
-        <v>1.211984825647145</v>
+        <v>1.219154344630031</v>
       </c>
       <c r="G1539">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="1540">
@@ -41883,10 +41883,10 @@
         <v>0.4607053674139334</v>
       </c>
       <c r="E1540">
-        <v>2.20420432952136</v>
+        <v>2.191241996366194</v>
       </c>
       <c r="F1540">
-        <v>0.2090120962215762</v>
+        <v>0.2102485111995552</v>
       </c>
       <c r="G1540">
         <v>6</v>
@@ -41906,8 +41906,17 @@
           <t>rural_interstate_poor_percent_score</t>
         </is>
       </c>
+      <c r="D1541">
+        <v>1.490372158032406</v>
+      </c>
       <c r="E1541">
-        <v>2.20420432952136</v>
+        <v>2.191241996366194</v>
+      </c>
+      <c r="F1541">
+        <v>0.68014950448373</v>
+      </c>
+      <c r="G1541">
+        <v>28</v>
       </c>
     </row>
     <row r="1542">
@@ -41928,10 +41937,10 @@
         <v>0.3065694171628117</v>
       </c>
       <c r="E1542">
-        <v>2.20420432952136</v>
+        <v>2.191241996366194</v>
       </c>
       <c r="F1542">
-        <v>0.1390839374811421</v>
+        <v>0.1399066911236666</v>
       </c>
       <c r="G1542">
         <v>4</v>
@@ -41955,10 +41964,10 @@
         <v>0.6388843010613818</v>
       </c>
       <c r="E1543">
-        <v>2.20420432952136</v>
+        <v>2.191241996366194</v>
       </c>
       <c r="F1543">
-        <v>0.2898480383622668</v>
+        <v>0.2915626398731239</v>
       </c>
       <c r="G1543">
         <v>14</v>
@@ -41982,10 +41991,10 @@
         <v>1.045386045442011</v>
       </c>
       <c r="E1544">
-        <v>2.20420432952136</v>
+        <v>2.191241996366194</v>
       </c>
       <c r="F1544">
-        <v>0.4742691189927093</v>
+        <v>0.477074666867287</v>
       </c>
       <c r="G1544">
         <v>21</v>
@@ -42009,10 +42018,10 @@
         <v>0.4820030293160084</v>
       </c>
       <c r="E1545">
-        <v>2.20420432952136</v>
+        <v>2.191241996366194</v>
       </c>
       <c r="F1545">
-        <v>0.218674386426178</v>
+        <v>0.219967958863206</v>
       </c>
       <c r="G1545">
         <v>8</v>
@@ -42036,10 +42045,10 @@
         <v>0.9468303298836719</v>
       </c>
       <c r="E1546">
-        <v>2.20420432952136</v>
+        <v>2.191241996366194</v>
       </c>
       <c r="F1546">
-        <v>0.4295565148850219</v>
+        <v>0.4320975645108256</v>
       </c>
       <c r="G1546">
         <v>18</v>
@@ -42063,10 +42072,10 @@
         <v>0.5443032484711802</v>
       </c>
       <c r="E1547">
-        <v>2.20420432952136</v>
+        <v>2.191241996366194</v>
       </c>
       <c r="F1547">
-        <v>0.2469386531825635</v>
+        <v>0.2483994234200583</v>
       </c>
       <c r="G1547">
         <v>11</v>
@@ -42090,13 +42099,13 @@
         <v>4.172191935563085</v>
       </c>
       <c r="E1548">
-        <v>2.20420432952136</v>
+        <v>2.191241996366194</v>
       </c>
       <c r="F1548">
-        <v>1.892833563424254</v>
+        <v>1.904030655893764</v>
       </c>
       <c r="G1548">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="1549">
@@ -42117,13 +42126,13 @@
         <v>1.919207069381429</v>
       </c>
       <c r="E1549">
-        <v>2.20420432952136</v>
+        <v>2.191241996366194</v>
       </c>
       <c r="F1549">
-        <v>0.8707028852439385</v>
+        <v>0.8758535445031225</v>
       </c>
       <c r="G1549">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1550">
@@ -42144,10 +42153,10 @@
         <v>1.376146788990826</v>
       </c>
       <c r="E1550">
-        <v>2.20420432952136</v>
+        <v>2.191241996366194</v>
       </c>
       <c r="F1550">
-        <v>0.6243281398914836</v>
+        <v>0.6280213647205253</v>
       </c>
       <c r="G1550">
         <v>26</v>
@@ -42171,10 +42180,10 @@
         <v>1.430943722780659</v>
       </c>
       <c r="E1551">
-        <v>2.20420432952136</v>
+        <v>2.191241996366194</v>
       </c>
       <c r="F1551">
-        <v>0.6491883277860115</v>
+        <v>0.6530286135231241</v>
       </c>
       <c r="G1551">
         <v>27</v>
@@ -46248,13 +46257,13 @@
         <v>3.841884334507866</v>
       </c>
       <c r="E1702">
-        <v>4.577575459088623</v>
+        <v>4.525431118153872</v>
       </c>
       <c r="F1702">
-        <v>0.8392836707650408</v>
+        <v>0.8489543281514237</v>
       </c>
       <c r="G1702">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="1703">
@@ -46275,13 +46284,13 @@
         <v>1.347849284788739</v>
       </c>
       <c r="E1703">
-        <v>4.577575459088623</v>
+        <v>4.525431118153872</v>
       </c>
       <c r="F1703">
-        <v>0.2944461094819594</v>
+        <v>0.2978388687393364</v>
       </c>
       <c r="G1703">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1704">
@@ -46302,13 +46311,13 @@
         <v>2.726697274576115</v>
       </c>
       <c r="E1704">
-        <v>4.577575459088623</v>
+        <v>4.525431118153872</v>
       </c>
       <c r="F1704">
-        <v>0.5956640800234869</v>
+        <v>0.6025276273983944</v>
       </c>
       <c r="G1704">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1705">
@@ -46329,13 +46338,13 @@
         <v>5.178207202683184</v>
       </c>
       <c r="E1705">
-        <v>4.577575459088623</v>
+        <v>4.525431118153872</v>
       </c>
       <c r="F1705">
-        <v>1.131211762419345</v>
+        <v>1.144246165168814</v>
       </c>
       <c r="G1705">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="1706">
@@ -46356,13 +46365,13 @@
         <v>10.15575488391877</v>
       </c>
       <c r="E1706">
-        <v>4.577575459088623</v>
+        <v>4.525431118153872</v>
       </c>
       <c r="F1706">
-        <v>2.218588196892497</v>
+        <v>2.244151909235503</v>
       </c>
       <c r="G1706">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="1707">
@@ -46383,13 +46392,13 @@
         <v>7.466878259495337</v>
       </c>
       <c r="E1707">
-        <v>4.577575459088623</v>
+        <v>4.525431118153872</v>
       </c>
       <c r="F1707">
-        <v>1.631186274531008</v>
+        <v>1.649981640321909</v>
       </c>
       <c r="G1707">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="1708">
@@ -46410,13 +46419,13 @@
         <v>1.578133383833602</v>
       </c>
       <c r="E1708">
-        <v>4.577575459088623</v>
+        <v>4.525431118153872</v>
       </c>
       <c r="F1708">
-        <v>0.3447531117592547</v>
+        <v>0.3487255341270985</v>
       </c>
       <c r="G1708">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1709">
@@ -46437,13 +46446,13 @@
         <v>7.784133300174085</v>
       </c>
       <c r="E1709">
-        <v>4.577575459088623</v>
+        <v>4.525431118153872</v>
       </c>
       <c r="F1709">
-        <v>1.700492623167784</v>
+        <v>1.720086572293158</v>
       </c>
       <c r="G1709">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1710">
@@ -46464,13 +46473,13 @@
         <v>1.178262761922527</v>
       </c>
       <c r="E1710">
-        <v>4.577575459088623</v>
+        <v>4.525431118153872</v>
       </c>
       <c r="F1710">
-        <v>0.2573988724933252</v>
+        <v>0.2603647544641434</v>
       </c>
       <c r="G1710">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1711">
@@ -46491,13 +46500,13 @@
         <v>1.619157279245838</v>
       </c>
       <c r="E1711">
-        <v>4.577575459088623</v>
+        <v>4.525431118153872</v>
       </c>
       <c r="F1711">
-        <v>0.3537150383902588</v>
+        <v>0.3577907246782636</v>
       </c>
       <c r="G1711">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1712">
@@ -46518,13 +46527,13 @@
         <v>16.35283180517326</v>
       </c>
       <c r="E1712">
-        <v>4.577575459088623</v>
+        <v>4.525431118153872</v>
       </c>
       <c r="F1712">
-        <v>3.572378424195119</v>
+        <v>3.613541202643324</v>
       </c>
       <c r="G1712">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="1713">
@@ -46545,13 +46554,13 @@
         <v>1.530150677638157</v>
       </c>
       <c r="E1713">
-        <v>4.577575459088623</v>
+        <v>4.525431118153872</v>
       </c>
       <c r="F1713">
-        <v>0.33427098937279</v>
+        <v>0.3381226313444309</v>
       </c>
       <c r="G1713">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1714">
@@ -46572,13 +46581,13 @@
         <v>4.657768866052593</v>
       </c>
       <c r="E1714">
-        <v>4.577575459088623</v>
+        <v>4.525431118153872</v>
       </c>
       <c r="F1714">
-        <v>1.017518751505177</v>
+        <v>1.029243125006996</v>
       </c>
       <c r="G1714">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="1715">
@@ -46599,13 +46608,13 @@
         <v>3.045702818771048</v>
       </c>
       <c r="E1715">
-        <v>4.577575459088623</v>
+        <v>4.525431118153872</v>
       </c>
       <c r="F1715">
-        <v>0.6653528371059196</v>
+        <v>0.6730193741217584</v>
       </c>
       <c r="G1715">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1716">
@@ -46626,13 +46635,13 @@
         <v>4.320012102222523</v>
       </c>
       <c r="E1716">
-        <v>4.577575459088623</v>
+        <v>4.525431118153872</v>
       </c>
       <c r="F1716">
-        <v>0.9437336731708669</v>
+        <v>0.9546078571150259</v>
       </c>
       <c r="G1716">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="1717">
@@ -46653,13 +46662,13 @@
         <v>2.485828216456696</v>
       </c>
       <c r="E1717">
-        <v>4.577575459088623</v>
+        <v>4.525431118153872</v>
       </c>
       <c r="F1717">
-        <v>0.5430447272084106</v>
+        <v>0.549301967382674</v>
       </c>
       <c r="G1717">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="1718">
@@ -46680,13 +46689,13 @@
         <v>4.770756685815098</v>
       </c>
       <c r="E1718">
-        <v>4.577575459088623</v>
+        <v>4.525431118153872</v>
       </c>
       <c r="F1718">
-        <v>1.04220164767419</v>
+        <v>1.054210430179149</v>
       </c>
       <c r="G1718">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="1719">
@@ -46707,13 +46716,13 @@
         <v>13.48845079546951</v>
       </c>
       <c r="E1719">
-        <v>4.577575459088623</v>
+        <v>4.525431118153872</v>
       </c>
       <c r="F1719">
-        <v>2.946636470773769</v>
+        <v>2.980589129146233</v>
       </c>
       <c r="G1719">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="1720">
@@ -46734,10 +46743,10 @@
         <v>0.6436781609195403</v>
       </c>
       <c r="E1720">
-        <v>4.577575459088623</v>
+        <v>4.525431118153872</v>
       </c>
       <c r="F1720">
-        <v>0.1406155216166975</v>
+        <v>0.1422357658560773</v>
       </c>
       <c r="G1720">
         <v>2</v>
@@ -46761,13 +46770,13 @@
         <v>6.917465610671113</v>
       </c>
       <c r="E1721">
-        <v>4.577575459088623</v>
+        <v>4.525431118153872</v>
       </c>
       <c r="F1721">
-        <v>1.51116364383174</v>
+        <v>1.528576047245872</v>
       </c>
       <c r="G1721">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="1722">
@@ -46788,13 +46797,13 @@
         <v>2.559868008757386</v>
       </c>
       <c r="E1722">
-        <v>4.577575459088623</v>
+        <v>4.525431118153872</v>
       </c>
       <c r="F1722">
-        <v>0.559219183088474</v>
+        <v>0.5656627936481932</v>
       </c>
       <c r="G1722">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1723">
@@ -46815,13 +46824,13 @@
         <v>6.155283854224003</v>
       </c>
       <c r="E1723">
-        <v>4.577575459088623</v>
+        <v>4.525431118153872</v>
       </c>
       <c r="F1723">
-        <v>1.34466027031906</v>
+        <v>1.360154136372099</v>
       </c>
       <c r="G1723">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="1724">
@@ -46842,13 +46851,13 @@
         <v>1.871311272284662</v>
       </c>
       <c r="E1724">
-        <v>4.577575459088623</v>
+        <v>4.525431118153872</v>
       </c>
       <c r="F1724">
-        <v>0.40879965584603</v>
+        <v>0.4135100553796638</v>
       </c>
       <c r="G1724">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="1725">
@@ -46869,13 +46878,13 @@
         <v>4.838151456579799</v>
       </c>
       <c r="E1725">
-        <v>4.577575459088623</v>
+        <v>4.525431118153872</v>
       </c>
       <c r="F1725">
-        <v>1.056924457023163</v>
+        <v>1.069102883296896</v>
       </c>
       <c r="G1725">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="1726">
@@ -46896,13 +46905,13 @@
         <v>3.2061503940556</v>
       </c>
       <c r="E1726">
-        <v>4.577575459088623</v>
+        <v>4.525431118153872</v>
       </c>
       <c r="F1726">
-        <v>0.700403613814797</v>
+        <v>0.7084740238767646</v>
       </c>
       <c r="G1726">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1727">
@@ -46923,13 +46932,13 @@
         <v>1.832571670732686</v>
       </c>
       <c r="E1727">
-        <v>4.577575459088623</v>
+        <v>4.525431118153872</v>
       </c>
       <c r="F1727">
-        <v>0.4003367475011637</v>
+        <v>0.4049496330595513</v>
       </c>
       <c r="G1727">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="1728">
@@ -46950,13 +46959,13 @@
         <v>1.278326554328879</v>
       </c>
       <c r="E1728">
-        <v>4.577575459088623</v>
+        <v>4.525431118153872</v>
       </c>
       <c r="F1728">
-        <v>0.2792584340233658</v>
+        <v>0.2824761930859674</v>
       </c>
       <c r="G1728">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1729">
@@ -46977,13 +46986,13 @@
         <v>2.693602693602694</v>
       </c>
       <c r="E1729">
-        <v>4.577575459088623</v>
+        <v>4.525431118153872</v>
       </c>
       <c r="F1729">
-        <v>0.5884343617437559</v>
+        <v>0.5952146045925314</v>
       </c>
       <c r="G1729">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1730">
@@ -47004,10 +47013,10 @@
         <v>0.103849924397255</v>
       </c>
       <c r="E1730">
-        <v>4.577575459088623</v>
+        <v>4.525431118153872</v>
       </c>
       <c r="F1730">
-        <v>0.02268666575251414</v>
+        <v>0.02294807316382712</v>
       </c>
       <c r="G1730">
         <v>1</v>
@@ -47031,13 +47040,13 @@
         <v>6.249579756305207</v>
       </c>
       <c r="E1731">
-        <v>4.577575459088623</v>
+        <v>4.525431118153872</v>
       </c>
       <c r="F1731">
-        <v>1.365259800119051</v>
+        <v>1.380991024531314</v>
       </c>
       <c r="G1731">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="1732">
@@ -47058,13 +47067,13 @@
         <v>4.317257834730335</v>
       </c>
       <c r="E1732">
-        <v>4.577575459088623</v>
+        <v>4.525431118153872</v>
       </c>
       <c r="F1732">
-        <v>0.9431319862043048</v>
+        <v>0.9539992372022977</v>
       </c>
       <c r="G1732">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="1733">
@@ -47085,13 +47094,13 @@
         <v>8.83566379056867</v>
       </c>
       <c r="E1733">
-        <v>4.577575459088623</v>
+        <v>4.525431118153872</v>
       </c>
       <c r="F1733">
-        <v>1.930206038007687</v>
+        <v>1.952446863045644</v>
       </c>
       <c r="G1733">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="1734">
@@ -47112,13 +47121,13 @@
         <v>2.715116558645373</v>
       </c>
       <c r="E1734">
-        <v>4.577575459088623</v>
+        <v>4.525431118153872</v>
       </c>
       <c r="F1734">
-        <v>0.5931342001702233</v>
+        <v>0.5999685969704898</v>
       </c>
       <c r="G1734">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1735">
@@ -47139,10 +47148,10 @@
         <v>0.6535040067964417</v>
       </c>
       <c r="E1735">
-        <v>4.577575459088623</v>
+        <v>4.525431118153872</v>
       </c>
       <c r="F1735">
-        <v>0.1427620391268333</v>
+        <v>0.1444070166430984</v>
       </c>
       <c r="G1735">
         <v>3</v>
@@ -47166,13 +47175,13 @@
         <v>2.982166541645014</v>
       </c>
       <c r="E1736">
-        <v>4.577575459088623</v>
+        <v>4.525431118153872</v>
       </c>
       <c r="F1736">
-        <v>0.6514729398341261</v>
+        <v>0.658979545546939</v>
       </c>
       <c r="G1736">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1737">
@@ -47193,13 +47202,13 @@
         <v>5.636682543164782</v>
       </c>
       <c r="E1737">
-        <v>4.577575459088623</v>
+        <v>4.525431118153872</v>
       </c>
       <c r="F1737">
-        <v>1.231368569134855</v>
+        <v>1.245557030037006</v>
       </c>
       <c r="G1737">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="1738">
@@ -47220,13 +47229,13 @@
         <v>2.48751973375432</v>
       </c>
       <c r="E1738">
-        <v>4.577575459088623</v>
+        <v>4.525431118153872</v>
       </c>
       <c r="F1738">
-        <v>0.5434142497455575</v>
+        <v>0.5496757477482259</v>
       </c>
       <c r="G1738">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1739">
@@ -47247,13 +47256,13 @@
         <v>5.686412198425039</v>
       </c>
       <c r="E1739">
-        <v>4.577575459088623</v>
+        <v>4.525431118153872</v>
       </c>
       <c r="F1739">
-        <v>1.242232323474834</v>
+        <v>1.256545962132506</v>
       </c>
       <c r="G1739">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="1740">
@@ -47274,13 +47283,13 @@
         <v>1.561008155893755</v>
       </c>
       <c r="E1740">
-        <v>4.577575459088623</v>
+        <v>4.525431118153872</v>
       </c>
       <c r="F1740">
-        <v>0.3410119985667141</v>
+        <v>0.3449413139074716</v>
       </c>
       <c r="G1740">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1741">
@@ -47297,8 +47306,17 @@
           <t>urban_interstate_poor_percent_score</t>
         </is>
       </c>
+      <c r="D1741">
+        <v>1.11074743901335</v>
+      </c>
       <c r="E1741">
-        <v>4.577575459088623</v>
+        <v>4.525431118153872</v>
+      </c>
+      <c r="F1741">
+        <v>0.2454456625265073</v>
+      </c>
+      <c r="G1741">
+        <v>5</v>
       </c>
     </row>
     <row r="1742">
@@ -47319,13 +47337,13 @@
         <v>1.5954597773194</v>
       </c>
       <c r="E1742">
-        <v>4.577575459088623</v>
+        <v>4.525431118153872</v>
       </c>
       <c r="F1742">
-        <v>0.3485381708239607</v>
+        <v>0.3525542065857939</v>
       </c>
       <c r="G1742">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1743">
@@ -47346,13 +47364,13 @@
         <v>1.592308278328465</v>
       </c>
       <c r="E1743">
-        <v>4.577575459088623</v>
+        <v>4.525431118153872</v>
       </c>
       <c r="F1743">
-        <v>0.3478497061511003</v>
+        <v>0.3518578090694793</v>
       </c>
       <c r="G1743">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1744">
@@ -47373,13 +47391,13 @@
         <v>4.518636501668191</v>
       </c>
       <c r="E1744">
-        <v>4.577575459088623</v>
+        <v>4.525431118153872</v>
       </c>
       <c r="F1744">
-        <v>0.9871244159823931</v>
+        <v>0.9984985703442875</v>
       </c>
       <c r="G1744">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1745">
@@ -47400,13 +47418,13 @@
         <v>2.367643780101138</v>
       </c>
       <c r="E1745">
-        <v>4.577575459088623</v>
+        <v>4.525431118153872</v>
       </c>
       <c r="F1745">
-        <v>0.5172265976304684</v>
+        <v>0.523186348059366</v>
       </c>
       <c r="G1745">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="1746">
@@ -47427,10 +47445,10 @@
         <v>0.7491278345377524</v>
       </c>
       <c r="E1746">
-        <v>4.577575459088623</v>
+        <v>4.525431118153872</v>
       </c>
       <c r="F1746">
-        <v>0.1636516625958365</v>
+        <v>0.1655373410795291</v>
       </c>
       <c r="G1746">
         <v>4</v>
@@ -47454,13 +47472,13 @@
         <v>2.685387422313179</v>
       </c>
       <c r="E1747">
-        <v>4.577575459088623</v>
+        <v>4.525431118153872</v>
       </c>
       <c r="F1747">
-        <v>0.5866396843292735</v>
+        <v>0.5933992479833987</v>
       </c>
       <c r="G1747">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1748">
@@ -47481,13 +47499,13 @@
         <v>3.654223968565815</v>
       </c>
       <c r="E1748">
-        <v>4.577575459088623</v>
+        <v>4.525431118153872</v>
       </c>
       <c r="F1748">
-        <v>0.7982880896721158</v>
+        <v>0.8074863749238854</v>
       </c>
       <c r="G1748">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1749">
@@ -47508,13 +47526,13 @@
         <v>3.768761269459659</v>
       </c>
       <c r="E1749">
-        <v>4.577575459088623</v>
+        <v>4.525431118153872</v>
       </c>
       <c r="F1749">
-        <v>0.8233094796890589</v>
+        <v>0.8327960742438848</v>
       </c>
       <c r="G1749">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1750">
@@ -47535,13 +47553,13 @@
         <v>4.704226906522459</v>
       </c>
       <c r="E1750">
-        <v>4.577575459088623</v>
+        <v>4.525431118153872</v>
       </c>
       <c r="F1750">
-        <v>1.027667801124365</v>
+        <v>1.039509117186945</v>
       </c>
       <c r="G1750">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1751">
@@ -47562,13 +47580,13 @@
         <v>7.453510802834312</v>
       </c>
       <c r="E1751">
-        <v>4.577575459088623</v>
+        <v>4.525431118153872</v>
       </c>
       <c r="F1751">
-        <v>1.628266069985939</v>
+        <v>1.647027787680688</v>
       </c>
       <c r="G1751">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="1752">
@@ -61220,10 +61238,10 @@
         <v>5</v>
       </c>
       <c r="H102">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I102">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J102">
         <v>5</v>
@@ -61272,10 +61290,10 @@
         <v>28</v>
       </c>
       <c r="H103">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I103">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J103">
         <v>50</v>
@@ -61324,10 +61342,10 @@
         <v>36</v>
       </c>
       <c r="H104">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I104">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J104">
         <v>42</v>
@@ -61376,10 +61394,10 @@
         <v>26</v>
       </c>
       <c r="H105">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I105">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J105">
         <v>25</v>
@@ -61428,10 +61446,10 @@
         <v>48</v>
       </c>
       <c r="H106">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I106">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J106">
         <v>39</v>
@@ -61480,10 +61498,10 @@
         <v>18</v>
       </c>
       <c r="H107">
+        <v>46</v>
+      </c>
+      <c r="I107">
         <v>45</v>
-      </c>
-      <c r="I107">
-        <v>44</v>
       </c>
       <c r="J107">
         <v>33</v>
@@ -61535,7 +61553,7 @@
         <v>1</v>
       </c>
       <c r="I108">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J108">
         <v>32</v>
@@ -61584,7 +61602,7 @@
         <v>23</v>
       </c>
       <c r="I109">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J109">
         <v>6</v>
@@ -61636,7 +61654,7 @@
         <v>2</v>
       </c>
       <c r="I110">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J110">
         <v>7</v>
@@ -61688,7 +61706,7 @@
         <v>16</v>
       </c>
       <c r="I111">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J111">
         <v>3</v>
@@ -61722,7 +61740,7 @@
         </is>
       </c>
       <c r="C112">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D112">
         <v>9</v>
@@ -61737,7 +61755,7 @@
         <v>6</v>
       </c>
       <c r="I112">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J112">
         <v>48</v>
@@ -61789,7 +61807,7 @@
         <v>22</v>
       </c>
       <c r="I113">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J113">
         <v>19</v>
@@ -61841,7 +61859,7 @@
         <v>25</v>
       </c>
       <c r="I114">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J114">
         <v>46</v>
@@ -61875,7 +61893,7 @@
         </is>
       </c>
       <c r="C115">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D115">
         <v>46</v>
@@ -61890,10 +61908,10 @@
         <v>3</v>
       </c>
       <c r="H115">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I115">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J115">
         <v>4</v>
@@ -61942,10 +61960,10 @@
         <v>19</v>
       </c>
       <c r="H116">
+        <v>33</v>
+      </c>
+      <c r="I116">
         <v>32</v>
-      </c>
-      <c r="I116">
-        <v>31</v>
       </c>
       <c r="J116">
         <v>38</v>
@@ -61997,7 +62015,7 @@
         <v>13</v>
       </c>
       <c r="I117">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J117">
         <v>8</v>
@@ -62049,7 +62067,7 @@
         <v>24</v>
       </c>
       <c r="I118">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J118">
         <v>15</v>
@@ -62098,10 +62116,10 @@
         <v>33</v>
       </c>
       <c r="H119">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I119">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J119">
         <v>47</v>
@@ -62202,10 +62220,10 @@
         <v>42</v>
       </c>
       <c r="H121">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I121">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J121">
         <v>30</v>
@@ -62239,7 +62257,7 @@
         </is>
       </c>
       <c r="C122">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D122">
         <v>6</v>
@@ -62254,10 +62272,10 @@
         <v>10</v>
       </c>
       <c r="H122">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I122">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J122">
         <v>17</v>
@@ -62306,10 +62324,10 @@
         <v>21</v>
       </c>
       <c r="H123">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I123">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J123">
         <v>16</v>
@@ -62361,7 +62379,7 @@
         <v>9</v>
       </c>
       <c r="I124">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J124">
         <v>22</v>
@@ -62410,10 +62428,10 @@
         <v>12</v>
       </c>
       <c r="H125">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I125">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J125">
         <v>34</v>
@@ -62465,7 +62483,7 @@
         <v>23</v>
       </c>
       <c r="I126">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J126">
         <v>13</v>
@@ -62514,10 +62532,10 @@
         <v>30</v>
       </c>
       <c r="H127">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I127">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J127">
         <v>26</v>
@@ -62569,7 +62587,7 @@
         <v>12</v>
       </c>
       <c r="I128">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J128">
         <v>44</v>
@@ -62621,7 +62639,7 @@
         <v>10</v>
       </c>
       <c r="I129">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J129">
         <v>2</v>
@@ -62725,7 +62743,7 @@
         <v>17</v>
       </c>
       <c r="I131">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J131">
         <v>31</v>
@@ -62774,10 +62792,10 @@
         <v>31</v>
       </c>
       <c r="H132">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I132">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J132">
         <v>35</v>
@@ -62826,10 +62844,10 @@
         <v>49</v>
       </c>
       <c r="H133">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I133">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J133">
         <v>28</v>
@@ -62863,7 +62881,7 @@
         </is>
       </c>
       <c r="C134">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D134">
         <v>8</v>
@@ -62881,7 +62899,7 @@
         <v>20</v>
       </c>
       <c r="I134">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J134">
         <v>20</v>
@@ -62967,7 +62985,7 @@
         </is>
       </c>
       <c r="C136">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D136">
         <v>10</v>
@@ -62985,7 +63003,7 @@
         <v>19</v>
       </c>
       <c r="I136">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J136">
         <v>9</v>
@@ -63034,10 +63052,10 @@
         <v>44</v>
       </c>
       <c r="H137">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I137">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J137">
         <v>45</v>
@@ -63089,7 +63107,7 @@
         <v>15</v>
       </c>
       <c r="I138">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J138">
         <v>24</v>
@@ -63138,10 +63156,10 @@
         <v>39</v>
       </c>
       <c r="H139">
+        <v>41</v>
+      </c>
+      <c r="I139">
         <v>40</v>
-      </c>
-      <c r="I139">
-        <v>39</v>
       </c>
       <c r="J139">
         <v>37</v>
@@ -63175,7 +63193,7 @@
         </is>
       </c>
       <c r="C140">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D140">
         <v>31</v>
@@ -63193,7 +63211,7 @@
         <v>6</v>
       </c>
       <c r="I140">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J140">
         <v>49</v>
@@ -63227,7 +63245,7 @@
         </is>
       </c>
       <c r="C141">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D141">
         <v>1</v>
@@ -63241,6 +63259,12 @@
       <c r="G141">
         <v>1</v>
       </c>
+      <c r="H141">
+        <v>28</v>
+      </c>
+      <c r="I141">
+        <v>5</v>
+      </c>
       <c r="J141">
         <v>21</v>
       </c>
@@ -63291,7 +63315,7 @@
         <v>4</v>
       </c>
       <c r="I142">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J142">
         <v>18</v>
@@ -63343,7 +63367,7 @@
         <v>14</v>
       </c>
       <c r="I143">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J143">
         <v>27</v>
@@ -63395,7 +63419,7 @@
         <v>21</v>
       </c>
       <c r="I144">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J144">
         <v>12</v>
@@ -63447,7 +63471,7 @@
         <v>8</v>
       </c>
       <c r="I145">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J145">
         <v>10</v>
@@ -63551,7 +63575,7 @@
         <v>11</v>
       </c>
       <c r="I147">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J147">
         <v>11</v>
@@ -63600,10 +63624,10 @@
         <v>50</v>
       </c>
       <c r="H148">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I148">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J148">
         <v>29</v>
@@ -63652,10 +63676,10 @@
         <v>8</v>
       </c>
       <c r="H149">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I149">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J149">
         <v>36</v>
@@ -63707,7 +63731,7 @@
         <v>26</v>
       </c>
       <c r="I150">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J150">
         <v>40</v>
@@ -63759,7 +63783,7 @@
         <v>27</v>
       </c>
       <c r="I151">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J151">
         <v>1</v>

--- a/AHR_combined_data.xlsx
+++ b/AHR_combined_data.xlsx
@@ -81214,13 +81214,13 @@
         <v>1.546558739611991</v>
       </c>
       <c r="G2452">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H2452">
-        <v>1.343662560004414</v>
+        <v>1.386367951805704</v>
       </c>
       <c r="I2452">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2453">
@@ -81247,13 +81247,13 @@
         <v>1.916588853159228</v>
       </c>
       <c r="G2453">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H2453">
-        <v>1.665147672023079</v>
+        <v>1.718070768831341</v>
       </c>
       <c r="I2453">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2454">
@@ -81280,13 +81280,13 @@
         <v>1.437964708203125</v>
       </c>
       <c r="G2454">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H2454">
-        <v>1.249315199954809</v>
+        <v>1.289021966136641</v>
       </c>
       <c r="I2454">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2455">
@@ -81313,13 +81313,13 @@
         <v>1.791750853497073</v>
       </c>
       <c r="G2455">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H2455">
-        <v>1.556687422880544</v>
+        <v>1.606163346587189</v>
       </c>
       <c r="I2455">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2456">
@@ -81346,13 +81346,13 @@
         <v>1.158444012988471</v>
       </c>
       <c r="G2456">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H2456">
-        <v>1.006465391999526</v>
+        <v>1.03845370527041</v>
       </c>
       <c r="I2456">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2457">
@@ -81379,13 +81379,13 @@
         <v>1.323958484081296</v>
       </c>
       <c r="G2457">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H2457">
-        <v>1.150265683737659</v>
+        <v>1.186824376494145</v>
       </c>
       <c r="I2457">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2458">
@@ -81412,10 +81412,10 @@
         <v>0.557401017424077</v>
       </c>
       <c r="G2458">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H2458">
-        <v>0.484274446768833</v>
+        <v>0.4996660566895171</v>
       </c>
       <c r="I2458">
         <v>3</v>
@@ -81445,10 +81445,10 @@
         <v>0.9435103377597176</v>
       </c>
       <c r="G2459">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H2459">
-        <v>0.8197293018064832</v>
+        <v>0.8457826146297031</v>
       </c>
       <c r="I2459">
         <v>18</v>
@@ -81478,13 +81478,13 @@
         <v>1.54518544526613</v>
       </c>
       <c r="G2460">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H2460">
-        <v>1.342469430930725</v>
+        <v>1.385136901719643</v>
       </c>
       <c r="I2460">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2461">
@@ -81511,10 +81511,10 @@
         <v>0.8306768720704029</v>
       </c>
       <c r="G2461">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H2461">
-        <v>0.7216986874631109</v>
+        <v>0.7446363104407784</v>
       </c>
       <c r="I2461">
         <v>13</v>
@@ -81544,13 +81544,13 @@
         <v>3.143211060938769</v>
       </c>
       <c r="G2462">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H2462">
-        <v>2.730846823079459</v>
+        <v>2.817640849347879</v>
       </c>
       <c r="I2462">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2463">
@@ -81577,13 +81577,13 @@
         <v>1.424057155134427</v>
       </c>
       <c r="G2463">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H2463">
-        <v>1.237232206996926</v>
+        <v>1.276554941529921</v>
       </c>
       <c r="I2463">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2464">
@@ -81610,10 +81610,10 @@
         <v>0.9563043256849029</v>
       </c>
       <c r="G2464">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H2464">
-        <v>0.8308448204918795</v>
+        <v>0.8572514158985873</v>
       </c>
       <c r="I2464">
         <v>20</v>
@@ -81643,13 +81643,13 @@
         <v>1.042099344822047</v>
       </c>
       <c r="G2465">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H2465">
-        <v>0.9053842169575864</v>
+        <v>0.9341598849465423</v>
       </c>
       <c r="I2465">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2466">
@@ -81676,10 +81676,10 @@
         <v>0.64135605439773</v>
       </c>
       <c r="G2466">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H2466">
-        <v>0.5572152520651036</v>
+        <v>0.5749251268248918</v>
       </c>
       <c r="I2466">
         <v>8</v>
@@ -81709,10 +81709,10 @@
         <v>0.9315724843391602</v>
       </c>
       <c r="G2467">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H2467">
-        <v>0.809357599602629</v>
+        <v>0.8350812704313139</v>
       </c>
       <c r="I2467">
         <v>17</v>
@@ -81742,13 +81742,13 @@
         <v>1.023625905976862</v>
       </c>
       <c r="G2468">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H2468">
-        <v>0.8893343460441584</v>
+        <v>0.9175999037970177</v>
       </c>
       <c r="I2468">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2469">
@@ -81775,13 +81775,13 @@
         <v>0.9691454880831557</v>
       </c>
       <c r="G2469">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H2469">
-        <v>0.8420013247354865</v>
+        <v>0.8687625053625003</v>
       </c>
       <c r="I2469">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2470">
@@ -81808,13 +81808,13 @@
         <v>1.077728692938083</v>
       </c>
       <c r="G2470">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H2470">
-        <v>0.9363392785887356</v>
+        <v>0.9660987858797161</v>
       </c>
       <c r="I2470">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2471">
@@ -81841,10 +81841,10 @@
         <v>0.5978690522960789</v>
       </c>
       <c r="G2471">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H2471">
-        <v>0.5194333980208908</v>
+        <v>0.535942458731107</v>
       </c>
       <c r="I2471">
         <v>7</v>
@@ -81874,10 +81874,10 @@
         <v>0.7424728473967344</v>
       </c>
       <c r="G2472">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H2472">
-        <v>0.6450663277860074</v>
+        <v>0.6655683578982627</v>
       </c>
       <c r="I2472">
         <v>11</v>
@@ -81907,10 +81907,10 @@
         <v>0.8125484229061878</v>
       </c>
       <c r="G2473">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H2473">
-        <v>0.7059485463342907</v>
+        <v>0.7283855853351079</v>
       </c>
       <c r="I2473">
         <v>12</v>
@@ -81940,10 +81940,10 @@
         <v>0.8978072570646936</v>
       </c>
       <c r="G2474">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H2474">
-        <v>0.7800221010168312</v>
+        <v>0.8048134068320945</v>
       </c>
       <c r="I2474">
         <v>15</v>
@@ -81973,13 +81973,13 @@
         <v>1.652932463280736</v>
       </c>
       <c r="G2475">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H2475">
-        <v>1.436080898992177</v>
+        <v>1.481723606674385</v>
       </c>
       <c r="I2475">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2476">
@@ -82006,13 +82006,13 @@
         <v>1.038530651512329</v>
       </c>
       <c r="G2476">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H2476">
-        <v>0.9022837077654113</v>
+        <v>0.9309608328137686</v>
       </c>
       <c r="I2476">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2477">
@@ -82039,13 +82039,13 @@
         <v>1.265166521633523</v>
       </c>
       <c r="G2477">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H2477">
-        <v>1.099186758154736</v>
+        <v>1.134122018365926</v>
       </c>
       <c r="I2477">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2478">
@@ -82072,13 +82072,13 @@
         <v>1.158331431633449</v>
       </c>
       <c r="G2478">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H2478">
-        <v>1.00636758042094</v>
+        <v>1.038352784963554</v>
       </c>
       <c r="I2478">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2479">
@@ -82105,13 +82105,13 @@
         <v>1.331149152665648</v>
       </c>
       <c r="G2479">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H2479">
-        <v>1.156512993917818</v>
+        <v>1.19327024383954</v>
       </c>
       <c r="I2479">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2480">
@@ -82138,10 +82138,10 @@
         <v>0.8989784599538359</v>
       </c>
       <c r="G2480">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H2480">
-        <v>0.7810396514221293</v>
+        <v>0.8058632978636996</v>
       </c>
       <c r="I2480">
         <v>16</v>
@@ -82171,13 +82171,13 @@
         <v>1.757109056582949</v>
       </c>
       <c r="G2481">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H2481">
-        <v>1.526590353605009</v>
+        <v>1.57510970743039</v>
       </c>
       <c r="I2481">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2482">
@@ -82204,13 +82204,13 @@
         <v>1.621249915389613</v>
       </c>
       <c r="G2482">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H2482">
-        <v>1.408554848854871</v>
+        <v>1.45332270090677</v>
       </c>
       <c r="I2482">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2483">
@@ -82237,10 +82237,10 @@
         <v>0.5653356515936899</v>
       </c>
       <c r="G2483">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H2483">
-        <v>0.4911681201793336</v>
+        <v>0.5067788305145926</v>
       </c>
       <c r="I2483">
         <v>4</v>
@@ -82270,13 +82270,13 @@
         <v>1.176656778823377</v>
       </c>
       <c r="G2484">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H2484">
-        <v>1.022288788123899</v>
+        <v>1.054780013622326</v>
       </c>
       <c r="I2484">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2485">
@@ -82303,10 +82303,10 @@
         <v>0.8899499884751475</v>
       </c>
       <c r="G2485">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H2485">
-        <v>0.7731956434389442</v>
+        <v>0.7977699851486677</v>
       </c>
       <c r="I2485">
         <v>14</v>
@@ -82336,10 +82336,10 @@
         <v>0.6690928544011803</v>
       </c>
       <c r="G2486">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H2486">
-        <v>0.5813132049875491</v>
+        <v>0.5997889807643001</v>
       </c>
       <c r="I2486">
         <v>9</v>
@@ -82369,10 +82369,10 @@
         <v>0.9574745409619284</v>
       </c>
       <c r="G2487">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H2487">
-        <v>0.8318615128518986</v>
+        <v>0.8583004216138107</v>
       </c>
       <c r="I2487">
         <v>21</v>
@@ -82402,13 +82402,13 @@
         <v>1.674049694553563</v>
       </c>
       <c r="G2488">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H2488">
-        <v>1.454427717839401</v>
+        <v>1.500653539251574</v>
       </c>
       <c r="I2488">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2489">
@@ -82435,10 +82435,10 @@
         <v>0.5812995077504219</v>
       </c>
       <c r="G2489">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H2489">
-        <v>0.5050376456501077</v>
+        <v>0.5210891686841483</v>
       </c>
       <c r="I2489">
         <v>6</v>
@@ -82468,10 +82468,10 @@
         <v>0.5727315192711556</v>
       </c>
       <c r="G2490">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H2490">
-        <v>0.4975937089671547</v>
+        <v>0.5134086426654111</v>
       </c>
       <c r="I2490">
         <v>5</v>
@@ -82501,13 +82501,13 @@
         <v>1.732935271076938</v>
       </c>
       <c r="G2491">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H2491">
-        <v>1.505587976077368</v>
+        <v>1.553439815016368</v>
       </c>
       <c r="I2491">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2492">
@@ -82534,13 +82534,13 @@
         <v>1.075570109353639</v>
       </c>
       <c r="G2492">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H2492">
-        <v>0.9344638839653246</v>
+        <v>0.9641637859174659</v>
       </c>
       <c r="I2492">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2493">
@@ -82555,13 +82555,25 @@
       <c r="C2493">
         <v>156</v>
       </c>
+      <c r="D2493">
+        <v>16164.75063</v>
+      </c>
       <c r="E2493" t="inlineStr">
         <is>
           <t>rural_fatalities_per_100m_VMT_score</t>
         </is>
       </c>
+      <c r="F2493">
+        <v>0.9650628306661357</v>
+      </c>
       <c r="G2493">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
+      </c>
+      <c r="H2493">
+        <v>0.8651027249376209</v>
+      </c>
+      <c r="I2493">
+        <v>22</v>
       </c>
     </row>
     <row r="2494">
@@ -82588,13 +82600,13 @@
         <v>1.337922335752768</v>
       </c>
       <c r="G2494">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H2494">
-        <v>1.162397589370366</v>
+        <v>1.199341868358666</v>
       </c>
       <c r="I2494">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2495">
@@ -82621,13 +82633,13 @@
         <v>1.180604144687008</v>
       </c>
       <c r="G2495">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H2495">
-        <v>1.025718291049169</v>
+        <v>1.05831851583839</v>
       </c>
       <c r="I2495">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2496">
@@ -82654,10 +82666,10 @@
         <v>0.5408658706973106</v>
       </c>
       <c r="G2496">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H2496">
-        <v>0.4699085794972739</v>
+        <v>0.4848436015746567</v>
       </c>
       <c r="I2496">
         <v>2</v>
@@ -82687,13 +82699,13 @@
         <v>1.25354972894032</v>
       </c>
       <c r="G2497">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H2497">
-        <v>1.089093996069861</v>
+        <v>1.12370847979146</v>
       </c>
       <c r="I2497">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2498">
@@ -82720,13 +82732,13 @@
         <v>1.053732927431458</v>
       </c>
       <c r="G2498">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H2498">
-        <v>0.9154915662554906</v>
+        <v>0.9445884743568733</v>
       </c>
       <c r="I2498">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2499">
@@ -82753,10 +82765,10 @@
         <v>0.711916799512206</v>
       </c>
       <c r="G2499">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H2499">
-        <v>0.6185189898333322</v>
+        <v>0.6381772705532205</v>
       </c>
       <c r="I2499">
         <v>10</v>
@@ -82786,10 +82798,10 @@
         <v>0.4906469365723513</v>
       </c>
       <c r="G2500">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H2500">
-        <v>0.4262779692535499</v>
+        <v>0.4398262872874848</v>
       </c>
       <c r="I2500">
         <v>1</v>
@@ -82819,10 +82831,10 @@
         <v>0.9495847396975362</v>
       </c>
       <c r="G2501">
-        <v>1.151002331721522</v>
+        <v>1.115547093827178</v>
       </c>
       <c r="H2501">
-        <v>0.8250067906267997</v>
+        <v>0.8512278369528403</v>
       </c>
       <c r="I2501">
         <v>19</v>
@@ -82852,10 +82864,10 @@
         <v>1.061679741146842</v>
       </c>
       <c r="G2502">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H2502">
-        <v>1.105390411122654</v>
+        <v>1.132780640519556</v>
       </c>
       <c r="I2502">
         <v>36</v>
@@ -82885,10 +82897,10 @@
         <v>1.261411418464348</v>
       </c>
       <c r="G2503">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H2503">
-        <v>1.313345288989801</v>
+        <v>1.345888387229848</v>
       </c>
       <c r="I2503">
         <v>45</v>
@@ -82918,10 +82930,10 @@
         <v>1.23537942968035</v>
       </c>
       <c r="G2504">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H2504">
-        <v>1.286241530983455</v>
+        <v>1.318113031078773</v>
       </c>
       <c r="I2504">
         <v>43</v>
@@ -82951,10 +82963,10 @@
         <v>0.9822082835756718</v>
       </c>
       <c r="G2505">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H2505">
-        <v>1.022647015207217</v>
+        <v>1.04798696393188</v>
       </c>
       <c r="I2505">
         <v>26</v>
@@ -82984,10 +82996,10 @@
         <v>0.9125068253040979</v>
       </c>
       <c r="G2506">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H2506">
-        <v>0.9500758615639947</v>
+        <v>0.9736175854027854</v>
       </c>
       <c r="I2506">
         <v>23</v>
@@ -83017,10 +83029,10 @@
         <v>1.191299959746605</v>
       </c>
       <c r="G2507">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H2507">
-        <v>1.240347254674201</v>
+        <v>1.271081550444724</v>
       </c>
       <c r="I2507">
         <v>41</v>
@@ -83050,10 +83062,10 @@
         <v>0.7196827190122299</v>
       </c>
       <c r="G2508">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H2508">
-        <v>0.7493129479775652</v>
+        <v>0.7678800110972188</v>
       </c>
       <c r="I2508">
         <v>19</v>
@@ -83083,10 +83095,10 @@
         <v>0.9913191410168661</v>
       </c>
       <c r="G2509">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H2509">
-        <v>1.032132977934284</v>
+        <v>1.05770797727322</v>
       </c>
       <c r="I2509">
         <v>27</v>
@@ -83116,10 +83128,10 @@
         <v>1.175569279528065</v>
       </c>
       <c r="G2510">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H2510">
-        <v>1.223968922866506</v>
+        <v>1.254297383503272</v>
       </c>
       <c r="I2510">
         <v>39</v>
@@ -83149,10 +83161,10 @@
         <v>1.031157054593156</v>
       </c>
       <c r="G2511">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H2511">
-        <v>1.073611067757111</v>
+        <v>1.100213843693129</v>
       </c>
       <c r="I2511">
         <v>32</v>
@@ -83182,10 +83194,10 @@
         <v>1.143791676866334</v>
       </c>
       <c r="G2512">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H2512">
-        <v>1.190882996942366</v>
+        <v>1.22039162859224</v>
       </c>
       <c r="I2512">
         <v>38</v>
@@ -83215,10 +83227,10 @@
         <v>0.6697451321627513</v>
       </c>
       <c r="G2513">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H2513">
-        <v>0.6973193688230925</v>
+        <v>0.7145980943148119</v>
       </c>
       <c r="I2513">
         <v>11</v>
@@ -83248,10 +83260,10 @@
         <v>0.9713350183635551</v>
       </c>
       <c r="G2514">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H2514">
-        <v>1.011326084198319</v>
+        <v>1.036385514027396</v>
       </c>
       <c r="I2514">
         <v>25</v>
@@ -83281,10 +83293,10 @@
         <v>0.6881759063033738</v>
       </c>
       <c r="G2515">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H2515">
-        <v>0.7165089607640709</v>
+        <v>0.7342631809950314</v>
       </c>
       <c r="I2515">
         <v>16</v>
@@ -83314,10 +83326,10 @@
         <v>0.6477854046018922</v>
       </c>
       <c r="G2516">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H2516">
-        <v>0.6744555320784841</v>
+        <v>0.6911677195153888</v>
       </c>
       <c r="I2516">
         <v>10</v>
@@ -83347,10 +83359,10 @@
         <v>0.6714571986417301</v>
       </c>
       <c r="G2517">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H2517">
-        <v>0.6991019231996349</v>
+        <v>0.7164248182198708</v>
       </c>
       <c r="I2517">
         <v>13</v>
@@ -83380,10 +83392,10 @@
         <v>0.9664382251635665</v>
       </c>
       <c r="G2518">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H2518">
-        <v>1.006227683956952</v>
+        <v>1.031160781631558</v>
       </c>
       <c r="I2518">
         <v>24</v>
@@ -83413,10 +83425,10 @@
         <v>1.199541949337344</v>
       </c>
       <c r="G2519">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H2519">
-        <v>1.2489285771852</v>
+        <v>1.279875507686167</v>
       </c>
       <c r="I2519">
         <v>42</v>
@@ -83446,10 +83458,10 @@
         <v>0.5028678933106425</v>
       </c>
       <c r="G2520">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H2520">
-        <v>0.5235715873475935</v>
+        <v>0.5365450542230532</v>
       </c>
       <c r="I2520">
         <v>3</v>
@@ -83479,10 +83491,10 @@
         <v>1.011113274179578</v>
       </c>
       <c r="G2521">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H2521">
-        <v>1.052742060076994</v>
+        <v>1.078827727395196</v>
       </c>
       <c r="I2521">
         <v>28</v>
@@ -83512,10 +83524,10 @@
         <v>0.5233313811194925</v>
       </c>
       <c r="G2522">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H2522">
-        <v>0.5448775822963089</v>
+        <v>0.5583789858023948</v>
       </c>
       <c r="I2522">
         <v>6</v>
@@ -83545,10 +83557,10 @@
         <v>0.8461012176731455</v>
       </c>
       <c r="G2523">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H2523">
-        <v>0.8809362528146218</v>
+        <v>0.9027647812746559</v>
       </c>
       <c r="I2523">
         <v>21</v>
@@ -83578,10 +83590,10 @@
         <v>0.3507276065045727</v>
       </c>
       <c r="G2524">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H2524">
-        <v>0.3651674964875611</v>
+        <v>0.3742159027306805</v>
       </c>
       <c r="I2524">
         <v>2</v>
@@ -83611,13 +83623,13 @@
         <v>1.500817967161366</v>
       </c>
       <c r="G2525">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H2525">
-        <v>1.562608501833805</v>
+        <v>1.601328039195548</v>
       </c>
       <c r="I2525">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2526">
@@ -83644,10 +83656,10 @@
         <v>1.023679431315542</v>
       </c>
       <c r="G2526">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H2526">
-        <v>1.065825581467118</v>
+        <v>1.09223544252591</v>
       </c>
       <c r="I2526">
         <v>31</v>
@@ -83677,13 +83689,13 @@
         <v>1.446432915893151</v>
       </c>
       <c r="G2527">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H2527">
-        <v>1.505984350641695</v>
+        <v>1.543300810434689</v>
       </c>
       <c r="I2527">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2528">
@@ -83710,10 +83722,10 @@
         <v>0.7859966683846932</v>
       </c>
       <c r="G2528">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H2528">
-        <v>0.8183571247844159</v>
+        <v>0.838635018595408</v>
       </c>
       <c r="I2528">
         <v>20</v>
@@ -83743,10 +83755,10 @@
         <v>1.182648816398851</v>
       </c>
       <c r="G2529">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H2529">
-        <v>1.231339933039217</v>
+        <v>1.26185103833934</v>
       </c>
       <c r="I2529">
         <v>40</v>
@@ -83776,10 +83788,10 @@
         <v>0.6796333690605267</v>
       </c>
       <c r="G2530">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H2530">
-        <v>0.7076147166818574</v>
+        <v>0.7251485483665879</v>
       </c>
       <c r="I2530">
         <v>14</v>
@@ -83809,10 +83821,10 @@
         <v>0.700370091056468</v>
       </c>
       <c r="G2531">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H2531">
-        <v>0.7292051952075838</v>
+        <v>0.7472740126798316</v>
       </c>
       <c r="I2531">
         <v>17</v>
@@ -83842,13 +83854,13 @@
         <v>1.38842927040198</v>
       </c>
       <c r="G2532">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H2532">
-        <v>1.445592623220356</v>
+        <v>1.481412649489863</v>
       </c>
       <c r="I2532">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2533">
@@ -83875,10 +83887,10 @@
         <v>0.7028487842852077</v>
       </c>
       <c r="G2533">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H2533">
-        <v>0.7317859393067448</v>
+        <v>0.7499187044776333</v>
       </c>
       <c r="I2533">
         <v>18</v>
@@ -83908,10 +83920,10 @@
         <v>0.891645867969482</v>
       </c>
       <c r="G2534">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H2534">
-        <v>0.9283560327768183</v>
+        <v>0.9513595656860007</v>
       </c>
       <c r="I2534">
         <v>22</v>
@@ -83941,10 +83953,10 @@
         <v>0.3302821603137818</v>
       </c>
       <c r="G2535">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H2535">
-        <v>0.3438802859526671</v>
+        <v>0.3524012210200789</v>
       </c>
       <c r="I2535">
         <v>1</v>
@@ -83974,10 +83986,10 @@
         <v>0.687999405488645</v>
       </c>
       <c r="G2536">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H2536">
-        <v>0.7163251931921798</v>
+        <v>0.7340748598863092</v>
       </c>
       <c r="I2536">
         <v>15</v>
@@ -84007,10 +84019,10 @@
         <v>1.072860645259916</v>
       </c>
       <c r="G2537">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H2537">
-        <v>1.117031646907113</v>
+        <v>1.144710331962207</v>
       </c>
       <c r="I2537">
         <v>37</v>
@@ -84040,10 +84052,10 @@
         <v>1.040451958710402</v>
       </c>
       <c r="G2538">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H2538">
-        <v>1.083288654589849</v>
+        <v>1.110131229352319</v>
       </c>
       <c r="I2538">
         <v>34</v>
@@ -84073,10 +84085,10 @@
         <v>1.01980536865182</v>
       </c>
       <c r="G2539">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H2539">
-        <v>1.061792018844983</v>
+        <v>1.088101933129862</v>
       </c>
       <c r="I2539">
         <v>30</v>
@@ -84106,10 +84118,10 @@
         <v>0.5037562395090401</v>
       </c>
       <c r="G2540">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H2540">
-        <v>0.524496507859315</v>
+        <v>0.5374928931396524</v>
       </c>
       <c r="I2540">
         <v>4</v>
@@ -84139,13 +84151,13 @@
         <v>1.310287011813789</v>
       </c>
       <c r="G2541">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H2541">
-        <v>1.364233151056419</v>
+        <v>1.398037188600351</v>
       </c>
       <c r="I2541">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2542">
@@ -84172,10 +84184,10 @@
         <v>0.5195600425309252</v>
       </c>
       <c r="G2542">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H2542">
-        <v>0.5409509730267414</v>
+        <v>0.5543550799328539</v>
       </c>
       <c r="I2542">
         <v>5</v>
@@ -84193,13 +84205,25 @@
       <c r="C2543">
         <v>415</v>
       </c>
+      <c r="D2543">
+        <v>31959.74724</v>
+      </c>
       <c r="E2543" t="inlineStr">
         <is>
           <t>urban_fatalities_per_100m_VMT_score</t>
         </is>
       </c>
+      <c r="F2543">
+        <v>1.298508392083266</v>
+      </c>
       <c r="G2543">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
+      </c>
+      <c r="H2543">
+        <v>1.38546975240875</v>
+      </c>
+      <c r="I2543">
+        <v>46</v>
       </c>
     </row>
     <row r="2544">
@@ -84226,10 +84250,10 @@
         <v>1.033397367658967</v>
       </c>
       <c r="G2544">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H2544">
-        <v>1.075943617286769</v>
+        <v>1.102604190961989</v>
       </c>
       <c r="I2544">
         <v>33</v>
@@ -84259,10 +84283,10 @@
         <v>0.5521000077874636</v>
       </c>
       <c r="G2545">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H2545">
-        <v>0.5748306489580042</v>
+        <v>0.589074253010385</v>
       </c>
       <c r="I2545">
         <v>7</v>
@@ -84292,10 +84316,10 @@
         <v>0.5689224355899444</v>
       </c>
       <c r="G2546">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H2546">
-        <v>0.5923456769499468</v>
+        <v>0.6070232820844478</v>
       </c>
       <c r="I2546">
         <v>8</v>
@@ -84325,10 +84349,10 @@
         <v>0.6701119199469469</v>
       </c>
       <c r="G2547">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H2547">
-        <v>0.6977012577146793</v>
+        <v>0.7149894459484665</v>
       </c>
       <c r="I2547">
         <v>12</v>
@@ -84358,10 +84382,10 @@
         <v>1.016886976352176</v>
       </c>
       <c r="G2548">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H2548">
-        <v>1.058753472719543</v>
+        <v>1.084988095528603</v>
       </c>
       <c r="I2548">
         <v>29</v>
@@ -84391,10 +84415,10 @@
         <v>1.238794342396874</v>
       </c>
       <c r="G2549">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H2549">
-        <v>1.289797039886346</v>
+        <v>1.32175664116609</v>
       </c>
       <c r="I2549">
         <v>44</v>
@@ -84424,10 +84448,10 @@
         <v>0.6403066259390674</v>
       </c>
       <c r="G2550">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H2550">
-        <v>0.66666884283464</v>
+        <v>0.6831880855865854</v>
       </c>
       <c r="I2550">
         <v>9</v>
@@ -84457,10 +84481,10 @@
         <v>1.051504159876637</v>
       </c>
       <c r="G2551">
-        <v>0.9604568037355969</v>
+        <v>0.9372333028748592</v>
       </c>
       <c r="H2551">
-        <v>1.094795888567732</v>
+        <v>1.121923598586675</v>
       </c>
       <c r="I2551">
         <v>35</v>
@@ -84490,10 +84514,10 @@
         <v>1.376907820757462</v>
       </c>
       <c r="G2552">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H2552">
-        <v>0.950295253754483</v>
+        <v>0.9709932027434547</v>
       </c>
       <c r="I2552">
         <v>29</v>
@@ -84523,10 +84547,10 @@
         <v>0.9856966282590103</v>
       </c>
       <c r="G2553">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H2553">
-        <v>0.6802945072684946</v>
+        <v>0.6951116927203739</v>
       </c>
       <c r="I2553">
         <v>7</v>
@@ -84556,13 +84580,13 @@
         <v>2.124589567809786</v>
       </c>
       <c r="G2554">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H2554">
-        <v>1.466319932263327</v>
+        <v>1.498257180228726</v>
       </c>
       <c r="I2554">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2555">
@@ -84589,10 +84613,10 @@
         <v>1.729944927007016</v>
       </c>
       <c r="G2555">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H2555">
-        <v>1.19394953576997</v>
+        <v>1.219954407928531</v>
       </c>
       <c r="I2555">
         <v>42</v>
@@ -84622,10 +84646,10 @@
         <v>1.657149781407989</v>
       </c>
       <c r="G2556">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H2556">
-        <v>1.143708785941803</v>
+        <v>1.16861938716404</v>
       </c>
       <c r="I2556">
         <v>39</v>
@@ -84655,10 +84679,10 @@
         <v>1.291920192878279</v>
       </c>
       <c r="G2557">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H2557">
-        <v>0.8916396646265115</v>
+        <v>0.9110600628891249</v>
       </c>
       <c r="I2557">
         <v>18</v>
@@ -84688,10 +84712,10 @@
         <v>1.453119341995307</v>
       </c>
       <c r="G2558">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H2558">
-        <v>1.002893870613157</v>
+        <v>1.024737446168535</v>
       </c>
       <c r="I2558">
         <v>32</v>
@@ -84721,10 +84745,10 @@
         <v>1.619642869533952</v>
       </c>
       <c r="G2559">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H2559">
-        <v>1.117822782681775</v>
+        <v>1.142169572632844</v>
       </c>
       <c r="I2559">
         <v>37</v>
@@ -84754,10 +84778,10 @@
         <v>1.192460724106906</v>
       </c>
       <c r="G2560">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H2560">
-        <v>0.8229960999016175</v>
+        <v>0.8409214038811818</v>
       </c>
       <c r="I2560">
         <v>14</v>
@@ -84787,10 +84811,10 @@
         <v>1.331335669055292</v>
       </c>
       <c r="G2561">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H2561">
-        <v>0.9188428944802592</v>
+        <v>0.9388557939277661</v>
       </c>
       <c r="I2561">
         <v>24</v>
@@ -84820,10 +84844,10 @@
         <v>0.6786476065228866</v>
       </c>
       <c r="G2562">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H2562">
-        <v>0.4683796472996711</v>
+        <v>0.4785812115071946</v>
       </c>
       <c r="I2562">
         <v>2</v>
@@ -84853,10 +84877,10 @@
         <v>1.293098669726099</v>
       </c>
       <c r="G2563">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H2563">
-        <v>0.8924530095274993</v>
+        <v>0.9118911228857154</v>
       </c>
       <c r="I2563">
         <v>19</v>
@@ -84886,10 +84910,10 @@
         <v>1.322136431171046</v>
       </c>
       <c r="G2564">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H2564">
-        <v>0.9124938913242251</v>
+        <v>0.9323685060197717</v>
       </c>
       <c r="I2564">
         <v>22</v>
@@ -84919,10 +84943,10 @@
         <v>1.028614968017167</v>
       </c>
       <c r="G2565">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H2565">
-        <v>0.7099152952082147</v>
+        <v>0.7253776375788172</v>
       </c>
       <c r="I2565">
         <v>10</v>
@@ -84952,10 +84976,10 @@
         <v>1.583484806397701</v>
       </c>
       <c r="G2566">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H2566">
-        <v>1.09286770924452</v>
+        <v>1.116670964083759</v>
       </c>
       <c r="I2566">
         <v>34</v>
@@ -84985,10 +85009,10 @@
         <v>1.319627999780003</v>
       </c>
       <c r="G2567">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H2567">
-        <v>0.9107626567351403</v>
+        <v>0.9305995641969917</v>
       </c>
       <c r="I2567">
         <v>21</v>
@@ -85018,10 +85042,10 @@
         <v>1.942203917118805</v>
       </c>
       <c r="G2568">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H2568">
-        <v>1.340443518757872</v>
+        <v>1.369639109774699</v>
       </c>
       <c r="I2568">
         <v>46</v>
@@ -85051,10 +85075,10 @@
         <v>1.613310347190545</v>
       </c>
       <c r="G2569">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H2569">
-        <v>1.113452289729006</v>
+        <v>1.137703887959569</v>
       </c>
       <c r="I2569">
         <v>36</v>
@@ -85084,10 +85108,10 @@
         <v>1.374254424733155</v>
       </c>
       <c r="G2570">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H2570">
-        <v>0.9484639694737076</v>
+        <v>0.9691220320921243</v>
       </c>
       <c r="I2570">
         <v>28</v>
@@ -85117,10 +85141,10 @@
         <v>1.116408646892007</v>
       </c>
       <c r="G2571">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H2571">
-        <v>0.7705075259201506</v>
+        <v>0.7872896001271995</v>
       </c>
       <c r="I2571">
         <v>12</v>
@@ -85150,10 +85174,10 @@
         <v>0.6589473424623987</v>
       </c>
       <c r="G2572">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H2572">
-        <v>0.4547831906943969</v>
+        <v>0.4646886166605317</v>
       </c>
       <c r="I2572">
         <v>1</v>
@@ -85183,10 +85207,10 @@
         <v>1.367814752575387</v>
       </c>
       <c r="G2573">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H2573">
-        <v>0.944019525339535</v>
+        <v>0.9645807855403769</v>
       </c>
       <c r="I2573">
         <v>27</v>
@@ -85216,10 +85240,10 @@
         <v>0.9749327334081804</v>
       </c>
       <c r="G2574">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H2574">
-        <v>0.6728656307420843</v>
+        <v>0.6875210112109528</v>
       </c>
       <c r="I2574">
         <v>6</v>
@@ -85249,10 +85273,10 @@
         <v>1.885996081543883</v>
       </c>
       <c r="G2575">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H2575">
-        <v>1.301650769842206</v>
+        <v>1.330001433627179</v>
       </c>
       <c r="I2575">
         <v>43</v>
@@ -85282,10 +85306,10 @@
         <v>1.016119235271226</v>
       </c>
       <c r="G2576">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H2576">
-        <v>0.7012911626834096</v>
+        <v>0.7165656667433741</v>
       </c>
       <c r="I2576">
         <v>9</v>
@@ -85315,10 +85339,10 @@
         <v>1.685846434514267</v>
       </c>
       <c r="G2577">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H2577">
-        <v>1.163514246288838</v>
+        <v>1.188856221240815</v>
       </c>
       <c r="I2577">
         <v>40</v>
@@ -85348,10 +85372,10 @@
         <v>1.326307566181995</v>
       </c>
       <c r="G2578">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H2578">
-        <v>0.9153726677709252</v>
+        <v>0.9353099837877813</v>
       </c>
       <c r="I2578">
         <v>23</v>
@@ -85381,10 +85405,10 @@
         <v>1.45342616195017</v>
       </c>
       <c r="G2579">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H2579">
-        <v>1.00310562737891</v>
+        <v>1.024953815112154</v>
       </c>
       <c r="I2579">
         <v>33</v>
@@ -85414,10 +85438,10 @@
         <v>1.197246280140075</v>
       </c>
       <c r="G2580">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H2580">
-        <v>0.8262989289772738</v>
+        <v>0.8442961703757161</v>
       </c>
       <c r="I2580">
         <v>16</v>
@@ -85447,10 +85471,10 @@
         <v>0.9487930017384785</v>
       </c>
       <c r="G2581">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H2581">
-        <v>0.6548248711751378</v>
+        <v>0.6690873140598569</v>
       </c>
       <c r="I2581">
         <v>5</v>
@@ -85480,10 +85504,10 @@
         <v>1.312811911777458</v>
       </c>
       <c r="G2582">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H2582">
-        <v>0.9060584231035613</v>
+        <v>0.9257928697908755</v>
       </c>
       <c r="I2582">
         <v>20</v>
@@ -85513,10 +85537,10 @@
         <v>1.194541570937952</v>
       </c>
       <c r="G2583">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H2583">
-        <v>0.8244322300749829</v>
+        <v>0.842388813753096</v>
       </c>
       <c r="I2583">
         <v>15</v>
@@ -85546,10 +85570,10 @@
         <v>1.429086850448325</v>
       </c>
       <c r="G2584">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H2584">
-        <v>0.98630745697769</v>
+        <v>1.007789771396616</v>
       </c>
       <c r="I2584">
         <v>30</v>
@@ -85579,10 +85603,10 @@
         <v>1.086157823037984</v>
       </c>
       <c r="G2585">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H2585">
-        <v>0.7496294294366646</v>
+        <v>0.7659567673138257</v>
       </c>
       <c r="I2585">
         <v>11</v>
@@ -85612,10 +85636,10 @@
         <v>1.346999624977847</v>
       </c>
       <c r="G2586">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H2586">
-        <v>0.9296536275909441</v>
+        <v>0.9499019907025851</v>
       </c>
       <c r="I2586">
         <v>26</v>
@@ -85645,10 +85669,10 @@
         <v>1.892020534142045</v>
       </c>
       <c r="G2587">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H2587">
-        <v>1.30580864346613</v>
+        <v>1.334249868006648</v>
       </c>
       <c r="I2587">
         <v>44</v>
@@ -85678,10 +85702,10 @@
         <v>1.625212381849401</v>
       </c>
       <c r="G2588">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H2588">
-        <v>1.12166667189448</v>
+        <v>1.146097183849346</v>
       </c>
       <c r="I2588">
         <v>38</v>
@@ -85711,10 +85735,10 @@
         <v>1.603578005470747</v>
       </c>
       <c r="G2589">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H2589">
-        <v>1.10673535631864</v>
+        <v>1.130840656075606</v>
       </c>
       <c r="I2589">
         <v>35</v>
@@ -85744,10 +85768,10 @@
         <v>0.9291123786127875</v>
       </c>
       <c r="G2590">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H2590">
-        <v>0.6412419700794157</v>
+        <v>0.6552085699691385</v>
       </c>
       <c r="I2590">
         <v>4</v>
@@ -85777,10 +85801,10 @@
         <v>1.911937498862678</v>
       </c>
       <c r="G2591">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H2591">
-        <v>1.319554659544971</v>
+        <v>1.348295279813793</v>
       </c>
       <c r="I2591">
         <v>45</v>
@@ -85810,10 +85834,10 @@
         <v>2.023549657207091</v>
       </c>
       <c r="G2592">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H2592">
-        <v>1.396585599987767</v>
+        <v>1.427003996157877</v>
       </c>
       <c r="I2592">
         <v>47</v>
@@ -85831,13 +85855,25 @@
       <c r="C2593">
         <v>625</v>
       </c>
+      <c r="D2593">
+        <v>30779.92565</v>
+      </c>
       <c r="E2593" t="inlineStr">
         <is>
           <t>other_fatalities_per_100m_VMT_score</t>
         </is>
       </c>
+      <c r="F2593">
+        <v>2.030544216080652</v>
+      </c>
       <c r="G2593">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
+      </c>
+      <c r="H2593">
+        <v>1.431936547938054</v>
+      </c>
+      <c r="I2593">
+        <v>48</v>
       </c>
     </row>
     <row r="2594">
@@ -85864,10 +85900,10 @@
         <v>1.722212539357844</v>
       </c>
       <c r="G2594">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H2594">
-        <v>1.188612903083</v>
+        <v>1.214501540470641</v>
       </c>
       <c r="I2594">
         <v>41</v>
@@ -85897,10 +85933,10 @@
         <v>0.8086699302884396</v>
       </c>
       <c r="G2595">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H2595">
-        <v>0.5581166618578144</v>
+        <v>0.5702727471917024</v>
       </c>
       <c r="I2595">
         <v>3</v>
@@ -85930,10 +85966,10 @@
         <v>0.9951797232199359</v>
       </c>
       <c r="G2596">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H2596">
-        <v>0.6868394189876488</v>
+        <v>0.7017991561868563</v>
       </c>
       <c r="I2596">
         <v>8</v>
@@ -85963,10 +85999,10 @@
         <v>1.332223226835592</v>
       </c>
       <c r="G2597">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H2597">
-        <v>0.9194554568706659</v>
+        <v>0.9394816982611732</v>
       </c>
       <c r="I2597">
         <v>25</v>
@@ -85996,10 +86032,10 @@
         <v>1.452483884490658</v>
       </c>
       <c r="G2598">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H2598">
-        <v>1.002455299314826</v>
+        <v>1.024289322548097</v>
       </c>
       <c r="I2598">
         <v>31</v>
@@ -86029,13 +86065,13 @@
         <v>2.078509820622562</v>
       </c>
       <c r="G2599">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H2599">
-        <v>1.434517247736388</v>
+        <v>1.465761815885224</v>
       </c>
       <c r="I2599">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2600">
@@ -86062,10 +86098,10 @@
         <v>1.176024938556992</v>
       </c>
       <c r="G2600">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H2600">
-        <v>0.8116526760613654</v>
+        <v>0.8293309140821361</v>
       </c>
       <c r="I2600">
         <v>13</v>
@@ -86095,10 +86131,10 @@
         <v>1.266123223323891</v>
       </c>
       <c r="G2601">
-        <v>1.44892633664905</v>
+        <v>1.418040638046829</v>
       </c>
       <c r="H2601">
-        <v>0.8738354678900174</v>
+        <v>0.8928680810359678</v>
       </c>
       <c r="I2601">
         <v>17</v>
@@ -97934,7 +97970,7 @@
         <v>9</v>
       </c>
       <c r="N152">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="O152">
         <v>36</v>
@@ -97986,7 +98022,7 @@
         <v>36</v>
       </c>
       <c r="N153">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="O153">
         <v>45</v>
@@ -98005,7 +98041,7 @@
         </is>
       </c>
       <c r="C154">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D154">
         <v>32</v>
@@ -98038,13 +98074,13 @@
         <v>2</v>
       </c>
       <c r="N154">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O154">
         <v>43</v>
       </c>
       <c r="P154">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="155">
@@ -98090,7 +98126,7 @@
         <v>22</v>
       </c>
       <c r="N155">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O155">
         <v>26</v>
@@ -98142,7 +98178,7 @@
         <v>24</v>
       </c>
       <c r="N156">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O156">
         <v>23</v>
@@ -98194,7 +98230,7 @@
         <v>18</v>
       </c>
       <c r="N157">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O157">
         <v>41</v>
@@ -98213,7 +98249,7 @@
         </is>
       </c>
       <c r="C158">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D158">
         <v>19</v>
@@ -98314,7 +98350,7 @@
         </is>
       </c>
       <c r="C160">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D160">
         <v>38</v>
@@ -98347,7 +98383,7 @@
         <v>6</v>
       </c>
       <c r="N160">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O160">
         <v>39</v>
@@ -98451,7 +98487,7 @@
         <v>30</v>
       </c>
       <c r="N162">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O162">
         <v>38</v>
@@ -98503,7 +98539,7 @@
         <v>19</v>
       </c>
       <c r="N163">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O163">
         <v>11</v>
@@ -98607,7 +98643,7 @@
         <v>20</v>
       </c>
       <c r="N165">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O165">
         <v>16</v>
@@ -98678,7 +98714,7 @@
         </is>
       </c>
       <c r="C167">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D167">
         <v>44</v>
@@ -98730,7 +98766,7 @@
         </is>
       </c>
       <c r="C168">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D168">
         <v>14</v>
@@ -98763,7 +98799,7 @@
         <v>33</v>
       </c>
       <c r="N168">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="O168">
         <v>24</v>
@@ -98815,7 +98851,7 @@
         <v>44</v>
       </c>
       <c r="N169">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O169">
         <v>42</v>
@@ -98867,7 +98903,7 @@
         <v>47</v>
       </c>
       <c r="N170">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O170">
         <v>3</v>
@@ -98938,7 +98974,7 @@
         </is>
       </c>
       <c r="C172">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D172">
         <v>6</v>
@@ -99042,7 +99078,7 @@
         </is>
       </c>
       <c r="C174">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D174">
         <v>25</v>
@@ -99127,10 +99163,10 @@
         <v>26</v>
       </c>
       <c r="N175">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O175">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P175">
         <v>43</v>
@@ -99146,7 +99182,7 @@
         </is>
       </c>
       <c r="C176">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D176">
         <v>4</v>
@@ -99179,7 +99215,7 @@
         <v>39</v>
       </c>
       <c r="N176">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O176">
         <v>31</v>
@@ -99198,7 +99234,7 @@
         </is>
       </c>
       <c r="C177">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D177">
         <v>18</v>
@@ -99231,10 +99267,10 @@
         <v>32</v>
       </c>
       <c r="N177">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O177">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="P177">
         <v>40</v>
@@ -99283,7 +99319,7 @@
         <v>37</v>
       </c>
       <c r="N178">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O178">
         <v>20</v>
@@ -99335,7 +99371,7 @@
         <v>1</v>
       </c>
       <c r="N179">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O179">
         <v>40</v>
@@ -99354,7 +99390,7 @@
         </is>
       </c>
       <c r="C180">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D180">
         <v>15</v>
@@ -99406,7 +99442,7 @@
         </is>
       </c>
       <c r="C181">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D181">
         <v>45</v>
@@ -99439,7 +99475,7 @@
         <v>25</v>
       </c>
       <c r="N181">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O181">
         <v>17</v>
@@ -99491,10 +99527,10 @@
         <v>13</v>
       </c>
       <c r="N182">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="O182">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="P182">
         <v>20</v>
@@ -99562,7 +99598,7 @@
         </is>
       </c>
       <c r="C184">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D184">
         <v>3</v>
@@ -99595,7 +99631,7 @@
         <v>31</v>
       </c>
       <c r="N184">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O184">
         <v>22</v>
@@ -99770,7 +99806,7 @@
         </is>
       </c>
       <c r="C188">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D188">
         <v>28</v>
@@ -99803,7 +99839,7 @@
         <v>15</v>
       </c>
       <c r="N188">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O188">
         <v>34</v>
@@ -99926,7 +99962,7 @@
         </is>
       </c>
       <c r="C191">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D191">
         <v>1</v>
@@ -99959,10 +99995,10 @@
         <v>27</v>
       </c>
       <c r="N191">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O191">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="P191">
         <v>45</v>
@@ -99978,7 +100014,7 @@
         </is>
       </c>
       <c r="C192">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D192">
         <v>34</v>
@@ -100011,7 +100047,7 @@
         <v>48</v>
       </c>
       <c r="N192">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="O192">
         <v>5</v>
@@ -100030,7 +100066,7 @@
         </is>
       </c>
       <c r="C193">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D193">
         <v>12</v>
@@ -100061,6 +100097,15 @@
       </c>
       <c r="M193">
         <v>11</v>
+      </c>
+      <c r="N193">
+        <v>22</v>
+      </c>
+      <c r="O193">
+        <v>46</v>
+      </c>
+      <c r="P193">
+        <v>48</v>
       </c>
     </row>
     <row r="194">
@@ -100073,7 +100118,7 @@
         </is>
       </c>
       <c r="C194">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D194">
         <v>41</v>
@@ -100106,7 +100151,7 @@
         <v>3</v>
       </c>
       <c r="N194">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O194">
         <v>33</v>
@@ -100158,7 +100203,7 @@
         <v>8</v>
       </c>
       <c r="N195">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O195">
         <v>7</v>
@@ -100229,7 +100274,7 @@
         </is>
       </c>
       <c r="C197">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D197">
         <v>2</v>
@@ -100262,7 +100307,7 @@
         <v>10</v>
       </c>
       <c r="N197">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O197">
         <v>12</v>
@@ -100314,7 +100359,7 @@
         <v>23</v>
       </c>
       <c r="N198">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O198">
         <v>29</v>
@@ -100372,7 +100417,7 @@
         <v>44</v>
       </c>
       <c r="P199">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="200">
@@ -100437,7 +100482,7 @@
         </is>
       </c>
       <c r="C201">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D201">
         <v>21</v>
